--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R3" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1559,6 +1559,1551 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133903424</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490160</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6671854</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133896512</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490170</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6671727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133896181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6671583</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133895909</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6672008</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133896123</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490124</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6671671</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133896038</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490090</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6671895</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133895881</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6672008</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133896156</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490181</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6671546</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133896144</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490176</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6671644</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133903494</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490166</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6671778</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133903222</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490160</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6671854</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133896368</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>490177</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6671694</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133896332</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490177</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6671694</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133903250</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92350</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490160</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6671854</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133896196</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490203</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6671578</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133896144</v>
+        <v>133903222</v>
       </c>
       <c r="B18" t="n">
         <v>57955</v>
@@ -2408,7 +2408,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490176</v>
+        <v>490160</v>
       </c>
       <c r="R18" t="n">
-        <v>6671644</v>
+        <v>6671854</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,12 +2447,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133903222</v>
+        <v>133896144</v>
       </c>
       <c r="B20" t="n">
         <v>57955</v>
@@ -2617,7 +2627,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2626,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490160</v>
+        <v>490176</v>
       </c>
       <c r="R20" t="n">
-        <v>6671854</v>
+        <v>6671644</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,22 +2666,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,7 +2900,7 @@
         <v>133903250</v>
       </c>
       <c r="B23" t="n">
-        <v>92350</v>
+        <v>92352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,6 +3104,200 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133923051</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93216</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490203</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6671578</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133922992</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93216</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Roskmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6671576</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133903222</v>
+        <v>133896144</v>
       </c>
       <c r="B18" t="n">
         <v>57955</v>
@@ -2408,7 +2408,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490160</v>
+        <v>490176</v>
       </c>
       <c r="R18" t="n">
-        <v>6671854</v>
+        <v>6671644</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,22 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,45 +2479,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903494</v>
+        <v>133903222</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490166</v>
+        <v>490160</v>
       </c>
       <c r="R19" t="n">
-        <v>6671778</v>
+        <v>6671854</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,50 +2591,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133896144</v>
+        <v>133903494</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490176</v>
+        <v>490166</v>
       </c>
       <c r="R20" t="n">
-        <v>6671644</v>
+        <v>6671778</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,12 +2656,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133896144</v>
+        <v>133903222</v>
       </c>
       <c r="B18" t="n">
         <v>57955</v>
@@ -2408,7 +2408,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490176</v>
+        <v>490160</v>
       </c>
       <c r="R18" t="n">
-        <v>6671644</v>
+        <v>6671854</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,12 +2447,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,50 +2489,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903222</v>
+        <v>133903494</v>
       </c>
       <c r="B19" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490160</v>
+        <v>490166</v>
       </c>
       <c r="R19" t="n">
-        <v>6671854</v>
+        <v>6671778</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,45 +2596,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133903494</v>
+        <v>133896144</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490166</v>
+        <v>490176</v>
       </c>
       <c r="R20" t="n">
-        <v>6671778</v>
+        <v>6671644</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,22 +2666,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133878054</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133878144</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>133877701</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>133877750</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>133882156</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>133877282</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>133903424</v>
       </c>
       <c r="B10" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>133896512</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>133896181</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>133895909</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>133896123</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>133896038</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>133895881</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>133896156</v>
       </c>
       <c r="B17" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,50 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133903222</v>
+        <v>133903494</v>
       </c>
       <c r="B18" t="n">
-        <v>57955</v>
+        <v>8460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490160</v>
+        <v>490166</v>
       </c>
       <c r="R18" t="n">
-        <v>6671854</v>
+        <v>6671778</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,45 +2484,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903494</v>
+        <v>133903222</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>57962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490166</v>
+        <v>490160</v>
       </c>
       <c r="R19" t="n">
-        <v>6671778</v>
+        <v>6671854</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,7 +2599,7 @@
         <v>133896144</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>133896368</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>133896332</v>
       </c>
       <c r="B22" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>133903250</v>
       </c>
       <c r="B23" t="n">
-        <v>92352</v>
+        <v>92343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>133896196</v>
       </c>
       <c r="B24" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>133923051</v>
       </c>
       <c r="B25" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>133922992</v>
       </c>
       <c r="B26" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R2" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133896181</v>
+        <v>133895909</v>
       </c>
       <c r="B12" t="n">
         <v>57962</v>
@@ -1806,14 +1806,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490214</v>
+        <v>490105</v>
       </c>
       <c r="R12" t="n">
-        <v>6671583</v>
+        <v>6672008</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133895909</v>
+        <v>133896181</v>
       </c>
       <c r="B13" t="n">
         <v>57962</v>
@@ -1908,14 +1908,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490105</v>
+        <v>490214</v>
       </c>
       <c r="R13" t="n">
-        <v>6672008</v>
+        <v>6671583</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133896123</v>
+        <v>133896038</v>
       </c>
       <c r="B14" t="n">
         <v>57962</v>
@@ -2005,7 +2005,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490124</v>
+        <v>490090</v>
       </c>
       <c r="R14" t="n">
-        <v>6671671</v>
+        <v>6671895</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133896038</v>
+        <v>133896123</v>
       </c>
       <c r="B15" t="n">
         <v>57962</v>
@@ -2107,7 +2107,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490090</v>
+        <v>490124</v>
       </c>
       <c r="R15" t="n">
-        <v>6671895</v>
+        <v>6671671</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R3" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
         <v>133878054</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133878144</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>133877701</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>133882156</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>133877282</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>133896512</v>
       </c>
       <c r="B11" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133895909</v>
+        <v>133896181</v>
       </c>
       <c r="B12" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,14 +1806,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490105</v>
+        <v>490214</v>
       </c>
       <c r="R12" t="n">
-        <v>6672008</v>
+        <v>6671583</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133896181</v>
+        <v>133895909</v>
       </c>
       <c r="B13" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,14 +1908,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490214</v>
+        <v>490105</v>
       </c>
       <c r="R13" t="n">
-        <v>6671583</v>
+        <v>6672008</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133896038</v>
+        <v>133896123</v>
       </c>
       <c r="B14" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490090</v>
+        <v>490124</v>
       </c>
       <c r="R14" t="n">
-        <v>6671895</v>
+        <v>6671671</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133896123</v>
+        <v>133896038</v>
       </c>
       <c r="B15" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490124</v>
+        <v>490090</v>
       </c>
       <c r="R15" t="n">
-        <v>6671671</v>
+        <v>6671895</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2278,7 +2278,7 @@
         <v>133896156</v>
       </c>
       <c r="B17" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,45 +2377,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133903494</v>
+        <v>133896144</v>
       </c>
       <c r="B18" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490166</v>
+        <v>490176</v>
       </c>
       <c r="R18" t="n">
-        <v>6671778</v>
+        <v>6671644</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2442,22 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,50 +2479,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903222</v>
+        <v>133903494</v>
       </c>
       <c r="B19" t="n">
-        <v>57962</v>
+        <v>8460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490160</v>
+        <v>490166</v>
       </c>
       <c r="R19" t="n">
-        <v>6671854</v>
+        <v>6671778</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2559,7 +2549,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2559,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133896144</v>
+        <v>133903222</v>
       </c>
       <c r="B20" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,7 +2617,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490176</v>
+        <v>490160</v>
       </c>
       <c r="R20" t="n">
-        <v>6671644</v>
+        <v>6671854</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,12 +2656,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,7 +2701,7 @@
         <v>133896368</v>
       </c>
       <c r="B21" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>133903250</v>
       </c>
       <c r="B23" t="n">
-        <v>92343</v>
+        <v>92353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>133923051</v>
       </c>
       <c r="B25" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>133922992</v>
       </c>
       <c r="B26" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -2377,50 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133896144</v>
+        <v>133903494</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490176</v>
+        <v>490166</v>
       </c>
       <c r="R18" t="n">
-        <v>6671644</v>
+        <v>6671778</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,12 +2442,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,45 +2484,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903494</v>
+        <v>133903222</v>
       </c>
       <c r="B19" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490166</v>
+        <v>490160</v>
       </c>
       <c r="R19" t="n">
-        <v>6671778</v>
+        <v>6671854</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2549,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2559,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133903222</v>
+        <v>133896144</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2617,7 +2627,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2626,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490160</v>
+        <v>490176</v>
       </c>
       <c r="R20" t="n">
-        <v>6671854</v>
+        <v>6671644</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,22 +2666,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,40 +2698,35 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133896368</v>
+        <v>133896332</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>
@@ -2800,35 +2795,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133896332</v>
+        <v>133896368</v>
       </c>
       <c r="B22" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R2" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2377,45 +2377,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133903494</v>
+        <v>133896144</v>
       </c>
       <c r="B18" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490166</v>
+        <v>490176</v>
       </c>
       <c r="R18" t="n">
-        <v>6671778</v>
+        <v>6671644</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2442,22 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,50 +2479,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903222</v>
+        <v>133903494</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490160</v>
+        <v>490166</v>
       </c>
       <c r="R19" t="n">
-        <v>6671854</v>
+        <v>6671778</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2559,7 +2549,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2559,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133896144</v>
+        <v>133903222</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2627,7 +2617,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490176</v>
+        <v>490160</v>
       </c>
       <c r="R20" t="n">
-        <v>6671644</v>
+        <v>6671854</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,12 +2656,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,35 +2698,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133896332</v>
+        <v>133896368</v>
       </c>
       <c r="B21" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>
@@ -2795,40 +2800,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133896368</v>
+        <v>133896332</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R3" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R2" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R3" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2377,50 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133896144</v>
+        <v>133903494</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490176</v>
+        <v>490166</v>
       </c>
       <c r="R18" t="n">
-        <v>6671644</v>
+        <v>6671778</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,12 +2442,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,45 +2484,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903494</v>
+        <v>133903222</v>
       </c>
       <c r="B19" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490166</v>
+        <v>490160</v>
       </c>
       <c r="R19" t="n">
-        <v>6671778</v>
+        <v>6671854</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2549,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2559,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133903222</v>
+        <v>133896144</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2617,7 +2627,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2626,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490160</v>
+        <v>490176</v>
       </c>
       <c r="R20" t="n">
-        <v>6671854</v>
+        <v>6671644</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,22 +2666,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,7 +2900,7 @@
         <v>133903250</v>
       </c>
       <c r="B23" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>133923051</v>
       </c>
       <c r="B25" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>133922992</v>
       </c>
       <c r="B26" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R2" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133896123</v>
+        <v>133896038</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -2005,7 +2005,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490124</v>
+        <v>490090</v>
       </c>
       <c r="R14" t="n">
-        <v>6671671</v>
+        <v>6671895</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133896038</v>
+        <v>133896123</v>
       </c>
       <c r="B15" t="n">
         <v>57972</v>
@@ -2107,7 +2107,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490090</v>
+        <v>490124</v>
       </c>
       <c r="R15" t="n">
-        <v>6671895</v>
+        <v>6671671</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133903222</v>
+        <v>133896144</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2408,7 +2408,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490160</v>
+        <v>490176</v>
       </c>
       <c r="R18" t="n">
-        <v>6671854</v>
+        <v>6671644</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,22 +2447,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133896144</v>
+        <v>133903222</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2627,7 +2617,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2636,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490176</v>
+        <v>490160</v>
       </c>
       <c r="R20" t="n">
-        <v>6671644</v>
+        <v>6671854</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2666,12 +2656,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,40 +2698,35 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133896368</v>
+        <v>133896332</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>
@@ -2800,35 +2795,40 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133896332</v>
+        <v>133896368</v>
       </c>
       <c r="B22" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877724</v>
+        <v>133877929</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490085</v>
+        <v>490103</v>
       </c>
       <c r="R2" t="n">
-        <v>6671983</v>
+        <v>6671949</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877929</v>
+        <v>133877724</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490103</v>
+        <v>490085</v>
       </c>
       <c r="R3" t="n">
-        <v>6671949</v>
+        <v>6671983</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133896038</v>
+        <v>133896123</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -2005,7 +2005,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490090</v>
+        <v>490124</v>
       </c>
       <c r="R14" t="n">
-        <v>6671895</v>
+        <v>6671671</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133896123</v>
+        <v>133896038</v>
       </c>
       <c r="B15" t="n">
         <v>57972</v>
@@ -2107,7 +2107,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490124</v>
+        <v>490090</v>
       </c>
       <c r="R15" t="n">
-        <v>6671671</v>
+        <v>6671895</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2698,35 +2698,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133896332</v>
+        <v>133896368</v>
       </c>
       <c r="B21" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>
@@ -2795,40 +2800,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133896368</v>
+        <v>133896332</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roskmora, Dlr</t>
@@ -2900,7 +2900,7 @@
         <v>133903250</v>
       </c>
       <c r="B23" t="n">
-        <v>92356</v>
+        <v>92363</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>133923051</v>
       </c>
       <c r="B25" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>133922992</v>
       </c>
       <c r="B26" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 23681-2026 artfynd.xlsx
+++ b/artfynd/A 23681-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133877929</v>
+        <v>133903250</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490103</v>
+        <v>490160</v>
       </c>
       <c r="R2" t="n">
-        <v>6671949</v>
+        <v>6671854</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133877724</v>
+        <v>133922992</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490085</v>
+        <v>490188</v>
       </c>
       <c r="R3" t="n">
-        <v>6671983</v>
+        <v>6671576</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133878054</v>
+        <v>133923051</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490103</v>
+        <v>490203</v>
       </c>
       <c r="R4" t="n">
-        <v>6671949</v>
+        <v>6671578</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,29 +949,19 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1006,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133878144</v>
+        <v>133877282</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1042,14 +1017,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490056</v>
+        <v>490128</v>
       </c>
       <c r="R5" t="n">
-        <v>6671860</v>
+        <v>6672106</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1081,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1100,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1230,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133877750</v>
+        <v>133877929</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1216,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>490103</v>
       </c>
       <c r="R7" t="n">
-        <v>6671984</v>
+        <v>6671949</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1337,27 +1317,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133882156</v>
+        <v>133878144</v>
       </c>
       <c r="B8" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1366,14 +1346,9 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1382,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490115</v>
+        <v>490056</v>
       </c>
       <c r="R8" t="n">
-        <v>6671699</v>
+        <v>6671860</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1415,14 +1390,19 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stöter en järpe</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,14 +1429,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133877282</v>
+        <v>133895909</v>
       </c>
       <c r="B9" t="n">
         <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1480,19 +1460,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långvasselbron, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490128</v>
+        <v>490105</v>
       </c>
       <c r="R9" t="n">
-        <v>6672106</v>
+        <v>6672008</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1522,19 +1502,9 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133903424</v>
+        <v>133896038</v>
       </c>
       <c r="B10" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,34 +1542,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490160</v>
+        <v>490090</v>
       </c>
       <c r="R10" t="n">
-        <v>6671854</v>
+        <v>6671895</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1626,22 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,14 +1633,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133896512</v>
+        <v>133896123</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1704,14 +1669,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490170</v>
+        <v>490124</v>
       </c>
       <c r="R11" t="n">
-        <v>6671727</v>
+        <v>6671671</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1770,14 +1735,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133896181</v>
+        <v>133896144</v>
       </c>
       <c r="B12" t="n">
         <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1806,14 +1771,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490214</v>
+        <v>490176</v>
       </c>
       <c r="R12" t="n">
-        <v>6671583</v>
+        <v>6671644</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1872,14 +1837,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133895909</v>
+        <v>133896156</v>
       </c>
       <c r="B13" t="n">
         <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1903,19 +1868,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490105</v>
+        <v>490181</v>
       </c>
       <c r="R13" t="n">
-        <v>6672008</v>
+        <v>6671546</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1974,14 +1939,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133896123</v>
+        <v>133896181</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2010,14 +1975,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490124</v>
+        <v>490214</v>
       </c>
       <c r="R14" t="n">
-        <v>6671671</v>
+        <v>6671583</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2076,14 +2041,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133896038</v>
+        <v>133896368</v>
       </c>
       <c r="B15" t="n">
         <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2107,19 +2072,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490090</v>
+        <v>490177</v>
       </c>
       <c r="R15" t="n">
-        <v>6671895</v>
+        <v>6671694</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2178,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133895881</v>
+        <v>133896512</v>
       </c>
       <c r="B16" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,34 +2154,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långvasslan, Dlr</t>
+          <t>Roskmora, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490105</v>
+        <v>490170</v>
       </c>
       <c r="R16" t="n">
-        <v>6672008</v>
+        <v>6671727</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2275,14 +2245,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133896156</v>
+        <v>133903222</v>
       </c>
       <c r="B17" t="n">
         <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2311,14 +2281,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490181</v>
+        <v>490160</v>
       </c>
       <c r="R17" t="n">
-        <v>6671546</v>
+        <v>6671854</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2345,12 +2315,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,14 +2357,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133896144</v>
+        <v>133903619</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2406,21 +2386,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490176</v>
+        <v>490195</v>
       </c>
       <c r="R18" t="n">
-        <v>6671644</v>
+        <v>6671761</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2447,12 +2422,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,45 +2464,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133903494</v>
+        <v>133878054</v>
       </c>
       <c r="B19" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490166</v>
+        <v>490103</v>
       </c>
       <c r="R19" t="n">
-        <v>6671778</v>
+        <v>6671949</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2544,29 +2534,29 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -2586,27 +2576,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133903222</v>
+        <v>133882156</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>57153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2615,9 +2605,14 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2626,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490160</v>
+        <v>490115</v>
       </c>
       <c r="R20" t="n">
-        <v>6671854</v>
+        <v>6671699</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2656,22 +2651,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stöter en järpe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,50 +2688,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133896368</v>
+        <v>133877724</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490177</v>
+        <v>490085</v>
       </c>
       <c r="R21" t="n">
-        <v>6671694</v>
+        <v>6671983</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2771,9 +2756,19 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133896332</v>
+        <v>133877750</v>
       </c>
       <c r="B22" t="n">
         <v>8460</v>
@@ -2831,14 +2826,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasselbron, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490177</v>
+        <v>490103</v>
       </c>
       <c r="R22" t="n">
-        <v>6671694</v>
+        <v>6671984</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2868,9 +2863,19 @@
           <t>2026-05-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133903250</v>
+        <v>133895881</v>
       </c>
       <c r="B23" t="n">
-        <v>92363</v>
+        <v>8460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2908,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490160</v>
+        <v>490105</v>
       </c>
       <c r="R23" t="n">
-        <v>6671854</v>
+        <v>6672008</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2962,27 +2967,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:51</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,10 +3096,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133923051</v>
+        <v>133896332</v>
       </c>
       <c r="B25" t="n">
-        <v>93264</v>
+        <v>8460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490203</v>
+        <v>490177</v>
       </c>
       <c r="R25" t="n">
-        <v>6671578</v>
+        <v>6671694</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3171,12 +3161,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133922992</v>
+        <v>133903321</v>
       </c>
       <c r="B26" t="n">
-        <v>93264</v>
+        <v>8460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,34 +3204,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Roskmora, Dlr</t>
+          <t>Långvasslan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490188</v>
+        <v>490160</v>
       </c>
       <c r="R26" t="n">
-        <v>6671576</v>
+        <v>6671854</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3271,9 +3261,19 @@
           <t>2026-05-28</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,6 +3297,113 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133903494</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långvasslan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490166</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6671778</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
